--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-location.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-location.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$93</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3284" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3594" uniqueCount="596">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T17:27:39+00:00</t>
+    <t>2026-02-05T18:16:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire</t>
+    <t>http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-pop-exp</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -269,10 +269,10 @@
 </t>
   </si>
   <si>
-    <t>A structured set of questions</t>
-  </si>
-  <si>
-    <t>A structured set of questions intended to guide the collection of answers from end-users. Questionnaires provide detailed control over order, presentation, phraseology and grouping to allow coherent, consistent data collection.</t>
+    <t>Populatable Questionnaire - Expression</t>
+  </si>
+  <si>
+    <t>Defines elements that support auto-population and pre-population of questionnaires using the Expression-based population mechanism.</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
@@ -486,58 +486,78 @@
 </t>
   </si>
   <si>
-    <t>Questionnaire.extension:designNote</t>
-  </si>
-  <si>
-    <t>designNote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {designNote}
+    <t>Questionnaire.extension:library</t>
+  </si>
+  <si>
+    <t>library</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {cqf-library}
 </t>
   </si>
   <si>
-    <t>Design comments</t>
-  </si>
-  <si>
-    <t>Information captured by the author/maintainer of the questionnaire for development purposes, not intended to be seen by users.</t>
-  </si>
-  <si>
-    <t>Allows capture of todos, rationale for design decisions, etc.  It can also be used to capture comments about the completion of the form in general. Allows commentary to be captured during the process of answering a questionnaire (if not already supported by the form design) as well as after the form is completed. Comments are not part of the "data" of the form. If a form prompts for a comment, this should be captured in an answer, not in this element. Formal assessments of the QuestionnaireResponse would use [[[Observation]]].</t>
-  </si>
-  <si>
-    <t>Questionnaire.extension:performerType</t>
-  </si>
-  <si>
-    <t>performerType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-performerType}
+    <t>A library containing logic used by the artifact</t>
+  </si>
+  <si>
+    <t>A reference to a library containing cql used in this Questionnaire.</t>
+  </si>
+  <si>
+    <t>For questionnaires, see additional guidance and examples in the [SDC implementation guide](http://hl7.org/fhir/uv/sdc/behavior.html#cqf-library).</t>
+  </si>
+  <si>
+    <t>Questionnaire.extension:launchContext</t>
+  </si>
+  <si>
+    <t>launchContext</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-launchContext}
 </t>
   </si>
   <si>
-    <t>Resource that can record answers to this Questionnaire</t>
-  </si>
-  <si>
-    <t>Indicates the types of resources that can record answers to a Questionnaire. Open Issue: Should this extension be moved to core?</t>
-  </si>
-  <si>
-    <t>Questionnaire.extension:assemble-expectation</t>
-  </si>
-  <si>
-    <t>assemble-expectation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-assemble-expectation}
+    <t>Context resources needed for Questionnaire</t>
+  </si>
+  <si>
+    <t>Resources that provide context for form processing logic (pre-population, flow-control, drop-down selection, etc.) when creating/displaying/editing a QuestionnaireResponse.</t>
+  </si>
+  <si>
+    <t>3 of these launch contexts are aligned with the existing SMART on FHIR "launch" contexts.</t>
+  </si>
+  <si>
+    <t>Questionnaire.extension:itemPopulationContext</t>
+  </si>
+  <si>
+    <t>itemPopulationContext</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-itemPopulationContext}
 </t>
   </si>
   <si>
-    <t>Questionnaire is modular</t>
-  </si>
-  <si>
-    <t>If present, indicates that this questionnaire has expectations with respect to assembly.  Specifically, indicates whether this form requires assembly (i.e. it can't be used directly without invoking the [$assemble](http://hl7.org/fhir/uv/sdc/2025Jan/OperationDefinition-Questionnaire-assemble.html) operation operation on it) and/or whether it is intended for use only as a 'child' in an assembly process.  The assembly processs might mean filling in item metadata based on information looked up from item.definitions and/or retrieving sub-questionnaires pointed to by [sub-questionnaire](http://hl7.org/fhir/uv/sdc/2025Jan/StructureDefinition-sdc-questionnaire-subQuestionnaire.html) extensions.</t>
-  </si>
-  <si>
-    <t>SDC-conformant Questionnaires **SHALL** declare this extension if they require an assembly process prior to use.  If not declared, then the Questionnaire is not necessarily safe for use as a child form and does not require assembly prior to use.</t>
+    <t>Establishes mapping context for a Questionnaire item</t>
+  </si>
+  <si>
+    <t>Specifies a query or other expression that identifies the resource (or set of resources for a repeating item) that should be used to support the population of this Questionnaire or Questionnaire.item on initial population.  When populating the questionnaire, it will set the specified variable name to that resource repetition for use in processing items within the group.</t>
+  </si>
+  <si>
+    <t>Questionnaire.extension:variable</t>
+  </si>
+  <si>
+    <t>variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {variable}
+</t>
+  </si>
+  <si>
+    <t>Variable for processing</t>
+  </si>
+  <si>
+    <t>Variable specifying a logic to generate a variable for use in subsequent logic.  The name of the variable will be added to FHIRPath's context when processing descendants of the element that contains this extension as well as extensions within the same element.</t>
+  </si>
+  <si>
+    <t>Ordering of variable extension declarations is significant as variables declared in one repetition of this extension might be used in subsequent extension repetitions
+For questionnaires, see additional guidance and examples in the [SDC implementation guide](http://hl7.org/fhir/uv/sdc/behavior.html#variable).</t>
   </si>
   <si>
     <t>Questionnaire.modifierExtension</t>
@@ -771,9 +791,6 @@
   </si>
   <si>
     <t>If none are specified, then the subject is unlimited.</t>
-  </si>
-  <si>
-    <t>A Questionnaire SHOULD specify the subject. However, it is optional to support legacy questionnaires.</t>
   </si>
   <si>
     <t>One of the resource types defined as part of this version of FHIR.</t>
@@ -1215,7 +1232,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-que-1:Group items must have nested items, display items cannot have nested items {(type='group' implies item.empty().not()) and (type.trace('type')='display' implies item.trace('item').empty())}que-3:Display items cannot have a "code" asserted {type!='display' or code.empty()}que-4:A question cannot have both answerOption and answerValueSet {answerOption.empty() or answerValueSet.empty()}que-5:Only 'choice' and 'open-choice' items can have answerValueSet {(type ='choice' or type = 'open-choice' or type = 'decimal' or type = 'integer' or type = 'date' or type = 'dateTime' or type = 'time' or type = 'string' or type = 'quantity') or (answerValueSet.empty() and answerOption.empty())}que-6:Required and repeat aren't permitted for display items {type!='display' or (required.empty() and repeats.empty())}que-8:Initial values can't be specified for groups or display items {(type!='group' and type!='display') or initial.empty()}que-9:Read-only can't be specified for "display" items {type!='display' or readOnly.empty()}que-10:Maximum length can only be declared for simple question types {(type in ('boolean' | 'decimal' | 'integer' | 'string' | 'text' | 'url' | 'open-choice')) or maxLength.empty()}que-11:If one or more answerOption is present, initial[x] must be missing {answerOption.empty() or initial.empty()}que-12:If there are more than one enableWhen, enableBehavior must be specified {enableWhen.count() &gt; 2 implies enableBehavior.exists()}que-13:Can only have multiple initial values for repeating items {repeats=true or initial.count() &lt;= 1}sdc-1:An item cannot have an answerExpression if answerOption or answerValueSet is already present. {extension('http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-answerExpression').empty().not() implies (answerOption.empty() and answerValueSet.empty())}que-1a:Group items must have nested items when Questionanire is complete {(type='group' and %resource.status='complete') implies item.empty().not()}que-1b:Groups should have items {type='group' implies item.empty().not()}que-1c:Display items cannot have child items {type='display' implies item.empty()}que-14:Can only have answerConstraint if answerOption, answerValueSet, or answerExpression are present. (This is a warning because other extensions may serve the same purpose) {extension('http://hl7.org/fhir/5.0/StructureDefinition/extension-Questionnaire.item.answerConstraint').exists() implies answerOption.exists() or answerValueSet.exists() or extension('http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-answerExpression').exists()}</t>
+que-1:Group items must have nested items, display items cannot have nested items {(type='group' implies item.empty().not()) and (type.trace('type')='display' implies item.trace('item').empty())}que-3:Display items cannot have a "code" asserted {type!='display' or code.empty()}que-4:A question cannot have both answerOption and answerValueSet {answerOption.empty() or answerValueSet.empty()}que-5:Only 'choice' and 'open-choice' items can have answerValueSet {(type ='choice' or type = 'open-choice' or type = 'decimal' or type = 'integer' or type = 'date' or type = 'dateTime' or type = 'time' or type = 'string' or type = 'quantity') or (answerValueSet.empty() and answerOption.empty())}que-6:Required and repeat aren't permitted for display items {type!='display' or (required.empty() and repeats.empty())}que-8:Initial values can't be specified for groups or display items {(type!='group' and type!='display') or initial.empty()}que-9:Read-only can't be specified for "display" items {type!='display' or readOnly.empty()}que-10:Maximum length can only be declared for simple question types {(type in ('boolean' | 'decimal' | 'integer' | 'string' | 'text' | 'url' | 'open-choice')) or maxLength.empty()}que-11:If one or more answerOption is present, initial[x] must be missing {answerOption.empty() or initial.empty()}que-12:If there are more than one enableWhen, enableBehavior must be specified {enableWhen.count() &gt; 2 implies enableBehavior.exists()}que-13:Can only have multiple initial values for repeating items {repeats=true or initial.count() &lt;= 1}sdc-1:An item cannot have an answerExpression if answerOption or answerValueSet is already present. {extension('http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-answerExpression').empty().not() implies (answerOption.empty() and answerValueSet.empty())}que-1a:Group items must have nested items when Questionanire is complete {(type='group' and %resource.status='complete') implies item.empty().not()}que-1b:Groups should have items {type='group' implies item.empty().not()}que-1c:Display items cannot have child items {type='display' implies item.empty()}que-14:Can only have answerConstraint if answerOption, answerValueSet, or answerExpression are present. (This is a warning because other extensions may serve the same purpose) {extension('http://hl7.org/fhir/5.0/StructureDefinition/extension-Questionnaire.item.answerConstraint').exists() implies answerOption.exists() or answerValueSet.exists() or extension('http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-answerExpression').exists()}sdc-pop-1:An item cannot have both initial.value and initialExpression {initial.empty() or extension('http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-initialExpression').empty()}</t>
   </si>
   <si>
     <t>./form_design/*[self::header or self::footer or self::section]</t>
@@ -1259,29 +1276,136 @@
 </t>
   </si>
   <si>
-    <t>Questionnaire.item.extension:designNote</t>
-  </si>
-  <si>
-    <t>Allows capture of todos, rationale for design decisions, etc.  It can also be used to capture comments about specific groups or questions within it. Allows commentary to be captured during the process of answering a questionnaire (if not already supported by the form design) as well as after the form is completed. Comments are not part of the "data" of the form. If a form prompts for a comment, this should be captured in an answer, not in this element. Formal assessments of the QuestionnaireResponse would use [[[Observation]]].</t>
-  </si>
-  <si>
-    <t>Questionnaire.item.extension:itemOptionalDisplay</t>
-  </si>
-  <si>
-    <t>itemOptionalDisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-optionalDisplay}
+    <t>Questionnaire.item.extension:unit</t>
+  </si>
+  <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {questionnaire-unit}
 </t>
   </si>
   <si>
-    <t>Can suppress from display to user</t>
-  </si>
-  <si>
-    <t>This extension is used when defining high-level questionnaires that will then be used as a basis for 'derived' Questionnaires that are further refined for use in specific organizations or contexts.  If the extension is present and set to 'true', it means that this item should be considered to be 'optional' from an adaptation perspective and that the question can be removed (i.e. not displayed) in derived questionnaires without impacting the validity of the instrument.  Alternatively, the element can be marked as 'hidden' and 'readOnly' and have a value or descendant item values declared using initialValue or initialExpression.  If the element with 'optionalDisplay=true' is marked as 'required=true', then this second approach is the only means to exclude the element from display.</t>
-  </si>
-  <si>
-    <t>If a group or question that contains other groups or questions is marked as "optional", all of its contents are automatically also treated as optional.</t>
+    <t>Unit for numeric answer</t>
+  </si>
+  <si>
+    <t>Provides a computable unit of measure associated with numeric questions to support subsequent computation on responses. This is for use on items of type integer and decimal, and it's purpose is to support converting the integer or decimal answer into a Quantity when extracting the data into a resource.</t>
+  </si>
+  <si>
+    <t>The human-readable unit is conveyed as a display element.  This element is for computation purposes.</t>
+  </si>
+  <si>
+    <t>N/A (MIF-level)</t>
+  </si>
+  <si>
+    <t>Questionnaire.item.extension:itemPopulationContext</t>
+  </si>
+  <si>
+    <t>Questionnaire.item.extension:itemVariable</t>
+  </si>
+  <si>
+    <t>itemVariable</t>
+  </si>
+  <si>
+    <t>Questionnaire.item.extension:initialExpression</t>
+  </si>
+  <si>
+    <t>initialExpression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-initialExpression}
+</t>
+  </si>
+  <si>
+    <t>Expression-determined initial value</t>
+  </si>
+  <si>
+    <t>Initial value for a question answer as determined by an evaluated expression.</t>
+  </si>
+  <si>
+    <t>Initial value is only calculated at the time the QuestionnaireResponse is first generated.  If the expression returns coded data, it **SHALL* return the information as either code or Coding, not CodeableConcept.  If the expression returns elements of type 'code', when the user selects one or more candidates, the code will be matched against the allowed Codings (from answerValueSet, answerOptions, or answerExpression).  In this case, it is an error if there is more than one Coding with the same code.</t>
+  </si>
+  <si>
+    <t>Questionnaire.item.extension:candidateExpression</t>
+  </si>
+  <si>
+    <t>candidateExpression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-candidateExpression}
+</t>
+  </si>
+  <si>
+    <t>Expression for possible answers</t>
+  </si>
+  <si>
+    <t>A FHIRPath or CQL expression, or FHIR Query that resolves to a list of candidate answers for the question item or that establishes context for a group item.  The user may select from among the candidates to choose answers for the question.</t>
+  </si>
+  <si>
+    <t>The results of the expression must correspond to the item type of the question the element appears on or must correspond to a resource, backbone element or complex data type for a group item.  Resources are considered a match for the Reference item type.  Quantity can be a match for decimal and integer items so long as a questionnaire-unit extension is present.  If the expression returns coded data, it **SHALL* return the information as either code or Coding, not CodeableConcept.  If the expression returns elements of type 'code', when the user selects one or more candidates, the code will be matched against the allowed Codings (from answerValueSet, answerOptions, or answerExpresssion).  In this case, it is an error if there is more than one Coding with the same code.</t>
+  </si>
+  <si>
+    <t>Questionnaire.item.extension:contextExpression</t>
+  </si>
+  <si>
+    <t>contextExpression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-contextExpression}
+</t>
+  </si>
+  <si>
+    <t>Expression for information to guide answers</t>
+  </si>
+  <si>
+    <t>A FHIR Query that resolves to one or more resources that can be displayed to the user to help provide context for answering a question. For example, if the question is "Has the patient discussed this issue on any visits in the past year?", the contextExpression might return the set of patient's encounters for the prior 12 month period to help jog the practitioner's memory.</t>
+  </si>
+  <si>
+    <t>Questionnaire.item.extension:itemHidden</t>
+  </si>
+  <si>
+    <t>itemHidden</t>
+  </si>
+  <si>
+    <t>Questionnaire.item.extension:choiceColumn</t>
+  </si>
+  <si>
+    <t>choiceColumn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-choiceColumn}
+</t>
+  </si>
+  <si>
+    <t>Guide for rendering multi-column choices</t>
+  </si>
+  <si>
+    <t>Provides guidelines for rendering multi-column choices.  I.e. when displaying a list of codes (for `choice` or `open-choice` items) or a list of resources (for `reference` items), this extension allows the drop-down to have multiple columns.  For codes, the author can pick additional code system properties to display - such as alternate display names strength or form for drug codes, etc.  For references, the author can choose particular columns from the resource (e.g. first name, last name, specialty, address).</t>
+  </si>
+  <si>
+    <t>Each repetition represents a column to display.</t>
+  </si>
+  <si>
+    <t>Questionnaire.item.extension:isSubject</t>
+  </si>
+  <si>
+    <t>isSubject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-isSubject}
+</t>
+  </si>
+  <si>
+    <t>Marks that this item identifies a different subject</t>
+  </si>
+  <si>
+    <t>If present and true, indicates that the item establishes a different subject for the group in a response.</t>
+  </si>
+  <si>
+    <t>The item type must be "reference" and there can only be one item with this extension in each group.</t>
+  </si>
+  <si>
+    <t>Allows the population process to leverage the fact that the subject for this group and descendants is distinct</t>
   </si>
   <si>
     <t>Questionnaire.item.modifierExtension</t>
@@ -1400,8 +1524,7 @@
     <t>The name of a section, the text of a question or text content for a display item.</t>
   </si>
   <si>
-    <t>When using this element to represent the name of a section, use group type item and also make sure to limit the text element to a short string suitable for display as a section heading.  Group item instructions should be included as a display type item within the group.
-This is optional only to support form assembly situations where the text may be generated from another source.  In an assembled Questionnaire, it should always be present.</t>
+    <t>When using this element to represent the name of a section, use group type item and also make sure to limit the text element to a short string suitable for display as a section heading.  Group item instructions should be included as a display type item within the group.</t>
   </si>
   <si>
     <t>Form Design/designation[context="primary?"/definition/  ./section_instruction/label</t>
@@ -2080,7 +2203,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP85"/>
+  <dimension ref="A1:AP93"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="66.78125" customWidth="true" bestFit="true"/>
@@ -3464,7 +3587,7 @@
         <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>81</v>
@@ -3606,7 +3729,9 @@
       <c r="M13" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="N13" s="2"/>
+      <c r="N13" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>81</v>
@@ -3690,13 +3815,13 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>133</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>81</v>
@@ -3718,17 +3843,15 @@
         <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N14" t="s" s="2">
         <v>166</v>
       </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>81</v>
@@ -3815,11 +3938,13 @@
         <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="D15" t="s" s="2">
-        <v>168</v>
+        <v>81</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3829,29 +3954,27 @@
         <v>80</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O15" t="s" s="2">
         <v>172</v>
       </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>81</v>
       </c>
@@ -3899,7 +4022,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3920,7 +4043,7 @@
         <v>81</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>81</v>
@@ -3934,33 +4057,33 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I16" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I16" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="J16" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>175</v>
@@ -4021,31 +4144,31 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>179</v>
+        <v>140</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>181</v>
+        <v>132</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>182</v>
+        <v>81</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>81</v>
@@ -4056,10 +4179,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4073,7 +4196,7 @@
         <v>89</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>81</v>
@@ -4082,19 +4205,19 @@
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O17" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>81</v>
@@ -4143,34 +4266,34 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>101</v>
+        <v>185</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>191</v>
+        <v>81</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>81</v>
@@ -4178,10 +4301,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4204,18 +4327,20 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="M18" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>81</v>
       </c>
@@ -4263,13 +4388,13 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>81</v>
@@ -4278,19 +4403,19 @@
         <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>81</v>
@@ -4298,10 +4423,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4309,7 +4434,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>89</v>
@@ -4324,20 +4449,18 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="M19" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>205</v>
-      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>81</v>
       </c>
@@ -4385,7 +4508,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4394,22 +4517,22 @@
         <v>89</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>206</v>
+        <v>81</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>81</v>
+        <v>203</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>81</v>
+        <v>204</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>132</v>
+        <v>205</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>81</v>
+        <v>206</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>81</v>
@@ -4446,7 +4569,7 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>208</v>
@@ -4457,7 +4580,9 @@
       <c r="N20" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="O20" s="2"/>
+      <c r="O20" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
       </c>
@@ -4514,7 +4639,7 @@
         <v>89</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>81</v>
+        <v>212</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>101</v>
@@ -4523,10 +4648,10 @@
         <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>211</v>
+        <v>81</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>212</v>
+        <v>132</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>81</v>
@@ -4551,10 +4676,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>90</v>
@@ -4563,21 +4688,21 @@
         <v>81</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>217</v>
-      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>81</v>
       </c>
@@ -4631,7 +4756,7 @@
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>81</v>
@@ -4643,10 +4768,10 @@
         <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>81</v>
@@ -4660,10 +4785,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4671,22 +4796,22 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>90</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>109</v>
+        <v>220</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>221</v>
@@ -4694,10 +4819,10 @@
       <c r="M22" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="N22" s="2"/>
+      <c r="O22" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>81</v>
       </c>
@@ -4721,13 +4846,13 @@
         <v>81</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>225</v>
+        <v>81</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>226</v>
+        <v>81</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>81</v>
@@ -4745,13 +4870,13 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>81</v>
@@ -4760,16 +4885,16 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>227</v>
+        <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>230</v>
+        <v>81</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>81</v>
@@ -4780,10 +4905,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4791,35 +4916,33 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>232</v>
+        <v>109</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>81</v>
       </c>
@@ -4843,13 +4966,13 @@
         <v>81</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>81</v>
+        <v>230</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>81</v>
+        <v>231</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>81</v>
+        <v>232</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>81</v>
@@ -4867,10 +4990,10 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>89</v>
@@ -4882,16 +5005,16 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>81</v>
+        <v>233</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>81</v>
@@ -4902,10 +5025,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4913,13 +5036,13 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G24" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G24" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="H24" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>81</v>
@@ -4928,7 +5051,7 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>109</v>
+        <v>238</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>239</v>
@@ -4937,10 +5060,10 @@
         <v>240</v>
       </c>
       <c r="N24" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="O24" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4965,13 +5088,13 @@
         <v>81</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>244</v>
+        <v>81</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>81</v>
@@ -4989,13 +5112,13 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>81</v>
@@ -5007,13 +5130,13 @@
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>246</v>
+        <v>132</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>81</v>
+        <v>243</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>81</v>
@@ -5024,21 +5147,21 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>248</v>
+        <v>81</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>90</v>
@@ -5050,16 +5173,16 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>249</v>
+        <v>109</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5085,13 +5208,13 @@
         <v>81</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>81</v>
+        <v>230</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>81</v>
+        <v>248</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>81</v>
+        <v>249</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>81</v>
@@ -5109,13 +5232,13 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>81</v>
@@ -5127,13 +5250,13 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>255</v>
+        <v>81</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>81</v>
@@ -5144,14 +5267,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>81</v>
+        <v>253</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5170,20 +5293,18 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>193</v>
+        <v>254</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="M26" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>260</v>
-      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>81</v>
       </c>
@@ -5231,7 +5352,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5249,13 +5370,13 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>81</v>
@@ -5266,10 +5387,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5280,10 +5401,10 @@
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>81</v>
@@ -5292,18 +5413,20 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O27" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="L27" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>81</v>
       </c>
@@ -5351,13 +5474,13 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>81</v>
@@ -5369,13 +5492,13 @@
         <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>81</v>
+        <v>268</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>81</v>
@@ -5386,10 +5509,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5400,28 +5523,28 @@
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J28" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="K28" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5471,13 +5594,13 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>81</v>
@@ -5489,10 +5612,10 @@
         <v>81</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
@@ -5506,10 +5629,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5520,7 +5643,7 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>90</v>
@@ -5529,23 +5652,21 @@
         <v>81</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M29" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>283</v>
-      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>81</v>
       </c>
@@ -5581,25 +5702,25 @@
         <v>81</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>284</v>
+        <v>81</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>285</v>
+        <v>81</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>81</v>
@@ -5611,10 +5732,10 @@
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>199</v>
+        <v>282</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
@@ -5628,10 +5749,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5642,28 +5763,32 @@
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>193</v>
+        <v>284</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="O30" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="M30" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>81</v>
       </c>
@@ -5699,40 +5824,40 @@
         <v>81</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>81</v>
+        <v>289</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>81</v>
+        <v>290</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>81</v>
+        <v>291</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>291</v>
+        <v>205</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>81</v>
@@ -5753,14 +5878,14 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>168</v>
+        <v>81</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>81</v>
@@ -5772,7 +5897,7 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>134</v>
+        <v>199</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>293</v>
@@ -5780,9 +5905,7 @@
       <c r="M31" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="N31" t="s" s="2">
-        <v>171</v>
-      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>81</v>
@@ -5819,40 +5942,40 @@
         <v>81</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="AC31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="AD31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AF31" t="s" s="2">
+      <c r="AG31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AG31" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>132</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
@@ -5873,14 +5996,14 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>81</v>
@@ -5889,19 +6012,19 @@
         <v>81</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M32" t="s" s="2">
-        <v>300</v>
-      </c>
       <c r="N32" t="s" s="2">
-        <v>301</v>
+        <v>177</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5927,41 +6050,43 @@
         <v>81</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="Y32" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z32" t="s" s="2">
-        <v>303</v>
+        <v>81</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>81</v>
+        <v>300</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>146</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>81</v>
@@ -5970,7 +6095,7 @@
         <v>81</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>305</v>
+        <v>132</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>81</v>
@@ -5979,15 +6104,15 @@
         <v>81</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>306</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6010,15 +6135,17 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>81</v>
@@ -6043,13 +6170,11 @@
         <v>81</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>81</v>
@@ -6067,7 +6192,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>89</v>
@@ -6088,7 +6213,7 @@
         <v>81</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>81</v>
@@ -6097,25 +6222,23 @@
         <v>81</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>81</v>
+        <v>311</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>316</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>89</v>
@@ -6130,20 +6253,16 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>279</v>
+        <v>313</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>81</v>
       </c>
@@ -6167,13 +6286,13 @@
         <v>81</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>81</v>
+        <v>316</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>81</v>
+        <v>317</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>81</v>
+        <v>318</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>81</v>
@@ -6191,16 +6310,16 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>278</v>
+        <v>319</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>101</v>
@@ -6209,10 +6328,10 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>286</v>
+        <v>81</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>199</v>
+        <v>296</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
@@ -6226,12 +6345,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="C35" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="D35" t="s" s="2">
         <v>81</v>
       </c>
@@ -6249,19 +6370,23 @@
         <v>81</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>193</v>
+        <v>284</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="O35" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>81</v>
       </c>
@@ -6309,28 +6434,28 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>81</v>
+        <v>291</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>291</v>
+        <v>205</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
@@ -6344,21 +6469,21 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>292</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>168</v>
+        <v>81</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>81</v>
@@ -6370,7 +6495,7 @@
         <v>81</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>134</v>
+        <v>199</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>293</v>
@@ -6378,9 +6503,7 @@
       <c r="M36" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="N36" t="s" s="2">
-        <v>171</v>
-      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6417,40 +6540,40 @@
         <v>81</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="AC36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="AD36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AF36" t="s" s="2">
+      <c r="AG36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>132</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
@@ -6464,21 +6587,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>297</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>81</v>
@@ -6487,19 +6610,19 @@
         <v>81</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M37" t="s" s="2">
-        <v>300</v>
-      </c>
       <c r="N37" t="s" s="2">
-        <v>301</v>
+        <v>177</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6510,7 +6633,7 @@
         <v>81</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>321</v>
+        <v>81</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>81</v>
@@ -6525,41 +6648,43 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="Y37" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z37" t="s" s="2">
-        <v>303</v>
+        <v>81</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>81</v>
+        <v>300</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>146</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>81</v>
@@ -6568,7 +6693,7 @@
         <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>305</v>
+        <v>132</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>81</v>
@@ -6577,15 +6702,15 @@
         <v>81</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>306</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6608,15 +6733,17 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>81</v>
@@ -6626,7 +6753,7 @@
         <v>81</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>81</v>
+        <v>326</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>81</v>
@@ -6641,29 +6768,29 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="AC38" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>89</v>
@@ -6684,7 +6811,7 @@
         <v>81</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>81</v>
@@ -6693,25 +6820,23 @@
         <v>81</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>81</v>
+        <v>311</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>89</v>
@@ -6726,13 +6851,13 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6759,29 +6884,29 @@
         <v>81</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y39" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="Z39" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB39" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AA39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>81</v>
-      </c>
+      <c r="AC39" s="2"/>
       <c r="AD39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>89</v>
@@ -6802,7 +6927,7 @@
         <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>81</v>
@@ -6819,9 +6944,11 @@
         <v>329</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="C40" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="D40" t="s" s="2">
         <v>81</v>
       </c>
@@ -6830,7 +6957,7 @@
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>81</v>
@@ -6842,17 +6969,15 @@
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6877,14 +7002,12 @@
         <v>81</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="Y40" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="Y40" s="2"/>
+      <c r="Z40" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="Z40" t="s" s="2">
-        <v>334</v>
-      </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
       </c>
@@ -6901,16 +7024,16 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>101</v>
@@ -6919,10 +7042,10 @@
         <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>335</v>
+        <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>199</v>
+        <v>296</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>81</v>
@@ -6936,10 +7059,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6950,28 +7073,28 @@
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J41" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="K41" t="s" s="2">
-        <v>272</v>
+        <v>331</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6997,13 +7120,13 @@
         <v>81</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>81</v>
+        <v>307</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>81</v>
+        <v>338</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>81</v>
+        <v>339</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>81</v>
@@ -7021,13 +7144,13 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
@@ -7042,13 +7165,13 @@
         <v>340</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>341</v>
+        <v>205</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>342</v>
+        <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>191</v>
+        <v>81</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>81</v>
@@ -7056,14 +7179,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>344</v>
+        <v>81</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7073,7 +7196,7 @@
         <v>89</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>81</v>
@@ -7082,18 +7205,18 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>81</v>
       </c>
@@ -7141,7 +7264,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7159,16 +7282,16 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>199</v>
+        <v>346</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>81</v>
+        <v>347</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>81</v>
@@ -7176,14 +7299,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>81</v>
+        <v>349</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7193,7 +7316,7 @@
         <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>81</v>
@@ -7202,18 +7325,18 @@
         <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" s="2"/>
+      <c r="O43" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="N43" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>81</v>
       </c>
@@ -7261,7 +7384,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7279,16 +7402,16 @@
         <v>81</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>355</v>
+        <v>205</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>81</v>
@@ -7296,10 +7419,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7322,20 +7445,18 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="N44" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>360</v>
-      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>81</v>
       </c>
@@ -7383,7 +7504,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7401,16 +7522,16 @@
         <v>81</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>81</v>
@@ -7418,10 +7539,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7441,22 +7562,22 @@
         <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -7505,7 +7626,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7523,16 +7644,16 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>199</v>
+        <v>367</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>81</v>
@@ -7540,10 +7661,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7554,10 +7675,10 @@
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>81</v>
@@ -7566,15 +7687,17 @@
         <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>298</v>
+        <v>369</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
         <v>373</v>
       </c>
@@ -7601,13 +7724,13 @@
         <v>81</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>311</v>
+        <v>81</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>374</v>
+        <v>81</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>375</v>
+        <v>81</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>81</v>
@@ -7625,13 +7748,13 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>81</v>
@@ -7643,16 +7766,16 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>81</v>
+        <v>374</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>376</v>
+        <v>205</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>81</v>
+        <v>197</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>81</v>
@@ -7660,10 +7783,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7674,30 +7797,30 @@
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J47" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="K47" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="L47" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>81</v>
       </c>
@@ -7721,13 +7844,13 @@
         <v>81</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>81</v>
+        <v>316</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>81</v>
+        <v>379</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>81</v>
+        <v>380</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>81</v>
@@ -7745,7 +7868,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7754,19 +7877,19 @@
         <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>382</v>
+        <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>383</v>
+        <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>384</v>
+        <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
@@ -7780,10 +7903,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7794,10 +7917,10 @@
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>81</v>
@@ -7806,15 +7929,17 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>193</v>
+        <v>383</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>288</v>
+        <v>384</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7863,28 +7988,28 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>290</v>
+        <v>382</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>81</v>
+        <v>387</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>81</v>
+        <v>388</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>81</v>
+        <v>389</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>291</v>
+        <v>390</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -7898,10 +8023,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7912,7 +8037,7 @@
         <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>81</v>
@@ -7924,13 +8049,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>134</v>
+        <v>199</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>135</v>
+        <v>293</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>136</v>
+        <v>294</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7969,38 +8094,40 @@
         <v>81</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AC49" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
@@ -8014,14 +8141,12 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="C50" t="s" s="2">
-        <v>389</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>81</v>
       </c>
@@ -8030,10 +8155,10 @@
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>81</v>
@@ -8042,17 +8167,15 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>390</v>
+        <v>134</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>391</v>
+        <v>135</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>81</v>
@@ -8089,19 +8212,17 @@
         <v>81</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8136,13 +8257,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="C51" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>81</v>
@@ -8155,7 +8276,7 @@
         <v>89</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>81</v>
@@ -8164,15 +8285,17 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="L51" t="s" s="2">
-        <v>144</v>
-      </c>
       <c r="M51" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -8221,7 +8344,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8230,7 +8353,7 @@
         <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>146</v>
+        <v>81</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>140</v>
@@ -8242,7 +8365,7 @@
         <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>81</v>
@@ -8256,13 +8379,13 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>151</v>
+        <v>400</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>81</v>
@@ -8284,17 +8407,15 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>152</v>
+        <v>401</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -8343,7 +8464,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8352,7 +8473,7 @@
         <v>80</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>140</v>
@@ -8364,7 +8485,7 @@
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
@@ -8378,13 +8499,13 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>81</v>
@@ -8397,7 +8518,7 @@
         <v>89</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>81</v>
@@ -8406,16 +8527,16 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8465,7 +8586,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8486,7 +8607,7 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>81</v>
+        <v>408</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
@@ -8500,46 +8621,44 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="C54" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="D54" t="s" s="2">
-        <v>406</v>
+        <v>81</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>407</v>
+        <v>165</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>172</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>81</v>
       </c>
@@ -8587,7 +8706,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>409</v>
+        <v>301</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8608,7 +8727,7 @@
         <v>81</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
@@ -8625,21 +8744,23 @@
         <v>410</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="C55" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="D55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>81</v>
@@ -8648,20 +8769,18 @@
         <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>411</v>
+        <v>170</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>412</v>
+        <v>171</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>414</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>81</v>
       </c>
@@ -8709,28 +8828,28 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>410</v>
+        <v>301</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>415</v>
+        <v>140</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>416</v>
+        <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>417</v>
+        <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
@@ -8744,12 +8863,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="C56" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="C56" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="D56" t="s" s="2">
         <v>81</v>
       </c>
@@ -8761,7 +8882,7 @@
         <v>89</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>81</v>
@@ -8770,20 +8891,18 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>103</v>
+        <v>414</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>417</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>81</v>
       </c>
@@ -8831,19 +8950,19 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>418</v>
+        <v>301</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>81</v>
@@ -8852,7 +8971,7 @@
         <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>
@@ -8866,12 +8985,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C57" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="D57" t="s" s="2">
         <v>81</v>
       </c>
@@ -8880,7 +9001,7 @@
         <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>81</v>
@@ -8892,20 +9013,18 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>298</v>
+        <v>420</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>428</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>81</v>
       </c>
@@ -8929,13 +9048,13 @@
         <v>81</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>311</v>
+        <v>81</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>374</v>
+        <v>81</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>375</v>
+        <v>81</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>81</v>
@@ -8953,7 +9072,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>424</v>
+        <v>301</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8962,10 +9081,10 @@
         <v>80</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>382</v>
+        <v>81</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>81</v>
@@ -8974,7 +9093,7 @@
         <v>81</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>376</v>
+        <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>81</v>
@@ -8988,24 +9107,26 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="C58" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="C58" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="D58" t="s" s="2">
-        <v>430</v>
+        <v>81</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>81</v>
@@ -9014,20 +9135,16 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>193</v>
+        <v>426</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>434</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>81</v>
       </c>
@@ -9075,28 +9192,28 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>429</v>
+        <v>301</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>435</v>
+        <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>436</v>
+        <v>81</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
@@ -9110,12 +9227,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="D59" t="s" s="2">
         <v>81</v>
       </c>
@@ -9127,7 +9246,7 @@
         <v>89</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>81</v>
@@ -9136,16 +9255,16 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>193</v>
+        <v>395</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>438</v>
+        <v>396</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>439</v>
+        <v>397</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>440</v>
+        <v>398</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9195,28 +9314,28 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>437</v>
+        <v>301</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>441</v>
+        <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>277</v>
+        <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>81</v>
@@ -9230,24 +9349,26 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="C60" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="D60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>81</v>
@@ -9256,20 +9377,18 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>109</v>
+        <v>433</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>81</v>
       </c>
@@ -9293,13 +9412,13 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>447</v>
+        <v>81</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>448</v>
+        <v>81</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -9317,28 +9436,28 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>442</v>
+        <v>301</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>449</v>
+        <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>450</v>
+        <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>81</v>
@@ -9352,12 +9471,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>451</v>
+        <v>437</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="C61" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="D61" t="s" s="2">
         <v>81</v>
       </c>
@@ -9366,31 +9487,31 @@
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>378</v>
+        <v>439</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -9439,7 +9560,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>451</v>
+        <v>301</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9451,7 +9572,7 @@
         <v>81</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>456</v>
+        <v>140</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>81</v>
@@ -9460,7 +9581,7 @@
         <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>450</v>
+        <v>81</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>81</v>
@@ -9474,42 +9595,46 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>457</v>
+        <v>444</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>457</v>
+        <v>444</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>81</v>
+        <v>445</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>193</v>
+        <v>134</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>288</v>
+        <v>446</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>81</v>
       </c>
@@ -9557,19 +9682,19 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>290</v>
+        <v>448</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>81</v>
+        <v>140</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>81</v>
@@ -9578,7 +9703,7 @@
         <v>81</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>291</v>
+        <v>132</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>81</v>
@@ -9592,24 +9717,24 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>168</v>
+        <v>81</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>81</v>
@@ -9618,18 +9743,20 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>134</v>
+        <v>199</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>293</v>
+        <v>450</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>294</v>
+        <v>451</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>453</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>81</v>
       </c>
@@ -9677,28 +9804,28 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>296</v>
+        <v>449</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>140</v>
+        <v>454</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>81</v>
+        <v>455</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>291</v>
+        <v>456</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>81</v>
@@ -9712,45 +9839,45 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>406</v>
+        <v>81</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>407</v>
+        <v>458</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>408</v>
+        <v>459</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>171</v>
+        <v>460</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>172</v>
+        <v>461</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -9799,19 +9926,19 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>409</v>
+        <v>457</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>81</v>
@@ -9820,7 +9947,7 @@
         <v>81</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>132</v>
+        <v>462</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>81</v>
@@ -9834,10 +9961,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9845,10 +9972,10 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>81</v>
@@ -9860,18 +9987,20 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>193</v>
+        <v>303</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>466</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>467</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>81</v>
       </c>
@@ -9895,13 +10024,13 @@
         <v>81</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>81</v>
+        <v>316</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>81</v>
+        <v>379</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>81</v>
+        <v>380</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>81</v>
@@ -9919,16 +10048,16 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>81</v>
+        <v>387</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>101</v>
@@ -9940,7 +10069,7 @@
         <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>450</v>
+        <v>381</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>81</v>
@@ -9954,24 +10083,24 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>81</v>
+        <v>469</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>81</v>
@@ -9980,16 +10109,20 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>109</v>
+        <v>199</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>471</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>81</v>
       </c>
@@ -10013,34 +10146,34 @@
         <v>81</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>467</v>
+        <v>81</v>
       </c>
       <c r="Z66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF66" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="AA66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>464</v>
-      </c>
       <c r="AG66" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>89</v>
@@ -10052,13 +10185,13 @@
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>81</v>
+        <v>474</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>81</v>
@@ -10072,10 +10205,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10083,13 +10216,13 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>81</v>
@@ -10098,15 +10231,17 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>470</v>
+        <v>199</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>478</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>479</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>81</v>
@@ -10131,13 +10266,13 @@
         <v>81</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>311</v>
+        <v>81</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>473</v>
+        <v>81</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>474</v>
+        <v>81</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>81</v>
@@ -10155,28 +10290,28 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>475</v>
+        <v>81</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>81</v>
+        <v>480</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>450</v>
+        <v>282</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>81</v>
@@ -10190,10 +10325,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10201,7 +10336,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>89</v>
@@ -10219,15 +10354,17 @@
         <v>109</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>484</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>81</v>
       </c>
@@ -10251,13 +10388,13 @@
         <v>81</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>81</v>
@@ -10275,28 +10412,28 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>481</v>
+        <v>81</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>81</v>
+        <v>488</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>450</v>
+        <v>489</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>81</v>
@@ -10310,10 +10447,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10324,36 +10461,36 @@
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>90</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>232</v>
+        <v>383</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>493</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>494</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q69" t="s" s="2">
-        <v>486</v>
-      </c>
+      <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
         <v>81</v>
       </c>
@@ -10397,28 +10534,28 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>487</v>
+        <v>81</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>101</v>
+        <v>495</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>488</v>
+        <v>81</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>450</v>
+        <v>489</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>81</v>
@@ -10432,10 +10569,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10449,7 +10586,7 @@
         <v>89</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>81</v>
@@ -10458,26 +10595,20 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>490</v>
+        <v>293</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>493</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q70" t="s" s="2">
-        <v>494</v>
-      </c>
+      <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
         <v>81</v>
       </c>
@@ -10521,7 +10652,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>489</v>
+        <v>295</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10530,19 +10661,19 @@
         <v>89</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>487</v>
+        <v>81</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>495</v>
+        <v>81</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>450</v>
+        <v>296</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>81</v>
@@ -10556,24 +10687,24 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>81</v>
@@ -10582,20 +10713,18 @@
         <v>81</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>232</v>
+        <v>134</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>497</v>
+        <v>298</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>498</v>
+        <v>299</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>500</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>81</v>
       </c>
@@ -10643,28 +10772,28 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>496</v>
+        <v>301</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>501</v>
+        <v>81</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>502</v>
+        <v>81</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>450</v>
+        <v>296</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
@@ -10678,44 +10807,46 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>81</v>
+        <v>445</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>504</v>
+        <v>134</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>505</v>
+        <v>446</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>506</v>
+        <v>447</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="O72" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
       </c>
@@ -10763,28 +10894,28 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>503</v>
+        <v>448</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>508</v>
+        <v>81</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>509</v>
+        <v>81</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>450</v>
+        <v>132</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>81</v>
@@ -10793,15 +10924,15 @@
         <v>81</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>132</v>
+        <v>81</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>510</v>
+        <v>499</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>510</v>
+        <v>499</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10809,13 +10940,13 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>81</v>
@@ -10824,16 +10955,16 @@
         <v>81</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>511</v>
+        <v>199</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10883,28 +11014,28 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>510</v>
+        <v>499</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>515</v>
+        <v>81</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>516</v>
+        <v>81</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>450</v>
+        <v>489</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>81</v>
@@ -10918,10 +11049,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>517</v>
+        <v>503</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>517</v>
+        <v>503</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10929,13 +11060,13 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>81</v>
@@ -10944,17 +11075,15 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>378</v>
+        <v>109</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>518</v>
+        <v>504</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>520</v>
-      </c>
+        <v>505</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -10979,13 +11108,13 @@
         <v>81</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>81</v>
+        <v>230</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>81</v>
+        <v>506</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>81</v>
+        <v>507</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>81</v>
@@ -11003,16 +11132,16 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>517</v>
+        <v>503</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>515</v>
+        <v>81</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>101</v>
@@ -11024,7 +11153,7 @@
         <v>81</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>450</v>
+        <v>489</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>81</v>
@@ -11038,10 +11167,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11049,7 +11178,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>89</v>
@@ -11064,13 +11193,13 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>193</v>
+        <v>509</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>288</v>
+        <v>510</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>289</v>
+        <v>511</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11097,13 +11226,13 @@
         <v>81</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>81</v>
+        <v>316</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>81</v>
+        <v>512</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>81</v>
+        <v>513</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>81</v>
@@ -11121,19 +11250,19 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>290</v>
+        <v>508</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>81</v>
+        <v>514</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>81</v>
@@ -11142,7 +11271,7 @@
         <v>81</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>291</v>
+        <v>489</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>81</v>
@@ -11156,24 +11285,24 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>168</v>
+        <v>81</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>81</v>
@@ -11182,16 +11311,16 @@
         <v>81</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>293</v>
+        <v>516</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>294</v>
+        <v>517</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>171</v>
+        <v>518</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11217,13 +11346,13 @@
         <v>81</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>81</v>
+        <v>230</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>81</v>
+        <v>517</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>81</v>
+        <v>519</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
@@ -11241,19 +11370,19 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>296</v>
+        <v>515</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>81</v>
+        <v>520</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>81</v>
@@ -11262,7 +11391,7 @@
         <v>81</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>291</v>
+        <v>489</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>81</v>
@@ -11276,50 +11405,50 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>406</v>
+        <v>81</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>134</v>
+        <v>238</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>407</v>
+        <v>522</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>408</v>
+        <v>523</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>172</v>
-      </c>
+        <v>524</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q77" s="2"/>
+      <c r="Q77" t="s" s="2">
+        <v>525</v>
+      </c>
       <c r="R77" t="s" s="2">
         <v>81</v>
       </c>
@@ -11363,28 +11492,28 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>409</v>
+        <v>521</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>81</v>
+        <v>526</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>81</v>
+        <v>527</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>132</v>
+        <v>489</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>81</v>
@@ -11398,10 +11527,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11409,7 +11538,7 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>89</v>
@@ -11424,87 +11553,91 @@
         <v>81</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>525</v>
+        <v>238</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="N78" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="P78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q78" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="R78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF78" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="O78" s="2"/>
-      <c r="P78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>524</v>
-      </c>
       <c r="AG78" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>81</v>
+        <v>526</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>81</v>
+        <v>534</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>450</v>
+        <v>489</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>81</v>
@@ -11518,10 +11651,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11544,24 +11677,24 @@
         <v>81</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="O79" s="2"/>
+        <v>538</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>539</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q79" t="s" s="2">
-        <v>533</v>
-      </c>
+      <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
         <v>81</v>
       </c>
@@ -11605,7 +11738,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11614,19 +11747,19 @@
         <v>89</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>81</v>
+        <v>540</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>81</v>
+        <v>541</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>450</v>
+        <v>489</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>81</v>
@@ -11640,10 +11773,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11654,10 +11787,10 @@
         <v>79</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>81</v>
@@ -11666,20 +11799,18 @@
         <v>81</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>378</v>
+        <v>543</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>538</v>
-      </c>
+        <v>546</v>
+      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>81</v>
       </c>
@@ -11727,28 +11858,28 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>81</v>
+        <v>548</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>450</v>
+        <v>489</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>81</v>
@@ -11757,15 +11888,15 @@
         <v>81</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>81</v>
+        <v>132</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11779,7 +11910,7 @@
         <v>89</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>81</v>
@@ -11788,15 +11919,17 @@
         <v>81</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>193</v>
+        <v>550</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>288</v>
+        <v>551</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>552</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>553</v>
+      </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>81</v>
@@ -11845,7 +11978,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>290</v>
+        <v>549</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11854,19 +11987,19 @@
         <v>89</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>81</v>
+        <v>554</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>81</v>
+        <v>555</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>291</v>
+        <v>489</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>81</v>
@@ -11880,14 +12013,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>541</v>
+        <v>556</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>541</v>
+        <v>556</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>168</v>
+        <v>81</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11897,7 +12030,7 @@
         <v>80</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>81</v>
@@ -11906,16 +12039,16 @@
         <v>81</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>134</v>
+        <v>383</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>293</v>
+        <v>557</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>294</v>
+        <v>558</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>171</v>
+        <v>559</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11965,7 +12098,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>296</v>
+        <v>556</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11974,10 +12107,10 @@
         <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>81</v>
+        <v>554</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>81</v>
@@ -11986,7 +12119,7 @@
         <v>81</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>291</v>
+        <v>489</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>81</v>
@@ -12000,46 +12133,42 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>542</v>
+        <v>560</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>542</v>
+        <v>560</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>406</v>
+        <v>81</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>134</v>
+        <v>199</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>407</v>
+        <v>293</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>172</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>81</v>
       </c>
@@ -12087,19 +12216,19 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>409</v>
+        <v>295</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>81</v>
@@ -12108,7 +12237,7 @@
         <v>81</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>132</v>
+        <v>296</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>81</v>
@@ -12122,24 +12251,24 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>543</v>
+        <v>561</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>543</v>
+        <v>561</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>81</v>
@@ -12148,16 +12277,16 @@
         <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>544</v>
+        <v>134</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>545</v>
+        <v>298</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>546</v>
+        <v>299</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>547</v>
+        <v>177</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12183,13 +12312,13 @@
         <v>81</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>311</v>
+        <v>81</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>473</v>
+        <v>81</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>474</v>
+        <v>81</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>81</v>
@@ -12207,28 +12336,28 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>543</v>
+        <v>301</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>548</v>
+        <v>81</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>450</v>
+        <v>296</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>81</v>
@@ -12242,14 +12371,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>81</v>
+        <v>445</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12259,28 +12388,28 @@
         <v>80</v>
       </c>
       <c r="H85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I85" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I85" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="J85" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>550</v>
+        <v>446</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>551</v>
+        <v>447</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>552</v>
+        <v>177</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>553</v>
+        <v>178</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>81</v>
@@ -12329,7 +12458,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>549</v>
+        <v>448</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12338,32 +12467,998 @@
         <v>80</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>554</v>
+        <v>81</v>
       </c>
       <c r="AJ85" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP85" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK85" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP85" t="s" s="2">
+      <c r="AK86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP86" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q87" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="R87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP87" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP88" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP89" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP90" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="P91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP91" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP92" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="P93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP93" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP85">
+  <autoFilter ref="A1:AP93">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12373,7 +13468,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI84">
+  <conditionalFormatting sqref="A2:AI92">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-location.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-location.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3594" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3593" uniqueCount="594">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T18:16:37+00:00</t>
+    <t>2026-02-06T16:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -511,17 +511,12 @@
     <t>launchContext</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/sdc/StructureDefinition/sdc-questionnaire-launchContext}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/ror/StructureDefinition/ror-launchcontext}
 </t>
   </si>
   <si>
-    <t>Context resources needed for Questionnaire</t>
-  </si>
-  <si>
-    <t>Resources that provide context for form processing logic (pre-population, flow-control, drop-down selection, etc.) when creating/displaying/editing a QuestionnaireResponse.</t>
-  </si>
-  <si>
-    <t>3 of these launch contexts are aligned with the existing SMART on FHIR "launch" contexts.</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}sdc-lcext-1:Types must be from the specified value set of resource types based on name: patient: Patient; user: Patient, Practitioner, PractitionerRole, Organization, RelatedPerson, Device; encounter: Encounter; location: Location; study: ResearchStudy; clinical: Any allowed clinical resource {(extension('name').value.where(code='patient' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Patient')) and (extension('name').value.where(code='user' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Patient' or value='Practitioner' or value='PractitionerRole' or value='RelatedPerson' or value='Organization' or value='Device')) and (extension('name').value.where(code='encounter' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Encounter')) and (extension('name').value.where(code='location' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Location')) and (extension('name').value.where(code='study' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'ResearchStudy'))}ror-inv-1:Types must be from the specified value set of resource types based on name: patient: Patient; user: Patient, Practitioner, PractitionerRole, Organization, RelatedPerson, Device; encounter: Encounter; location: Location; study: ResearchStudy; clinical: Any allowed clinical resource; ror-structure: Location, HealthcareServive, Organization {(extension('name').value.where(code='patient' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Patient')) and (extension('name').value.where(code='user' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Patient' or value='Practitioner' or value='PractitionerRole' or value='RelatedPerson' or value='Organization' or value='Device')) and (extension('name').value.where(code='encounter' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Encounter')) and (extension('name').value.where(code='location' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Location')) and (extension('name').value.where(code='study' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'ResearchStudy')) and (extension('name').value.where(code='ror-structure' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Location' or value='HealthcareService' or value='Organization'))}</t>
   </si>
   <si>
     <t>Questionnaire.extension:itemPopulationContext</t>
@@ -3226,7 +3221,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>80</v>
@@ -3706,10 +3701,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>90</v>
@@ -3724,14 +3719,12 @@
         <v>158</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>81</v>
@@ -3789,10 +3782,10 @@
         <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>81</v>
@@ -3815,13 +3808,13 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>133</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>81</v>
@@ -3843,13 +3836,13 @@
         <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3935,13 +3928,13 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>133</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>81</v>
@@ -3963,16 +3956,16 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4057,14 +4050,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4086,16 +4079,16 @@
         <v>134</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>81</v>
@@ -4144,7 +4137,7 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -4179,10 +4172,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4208,16 +4201,16 @@
         <v>103</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>81</v>
@@ -4266,7 +4259,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -4278,19 +4271,19 @@
         <v>81</v>
       </c>
       <c r="AJ17" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AK17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>81</v>
@@ -4301,10 +4294,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4327,19 +4320,19 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>81</v>
@@ -4388,7 +4381,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4406,16 +4399,16 @@
         <v>81</v>
       </c>
       <c r="AL18" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>81</v>
@@ -4423,10 +4416,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4449,16 +4442,16 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4508,7 +4501,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4523,16 +4516,16 @@
         <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>81</v>
@@ -4543,10 +4536,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4569,19 +4562,19 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -4630,7 +4623,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4639,7 +4632,7 @@
         <v>89</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>101</v>
@@ -4665,10 +4658,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4691,16 +4684,16 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4750,7 +4743,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4768,10 +4761,10 @@
         <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>81</v>
@@ -4785,10 +4778,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4811,17 +4804,17 @@
         <v>81</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -4870,7 +4863,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4888,10 +4881,10 @@
         <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>81</v>
@@ -4905,10 +4898,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4934,13 +4927,13 @@
         <v>109</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4966,14 +4959,14 @@
         <v>81</v>
       </c>
       <c r="X23" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="Z23" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="Y23" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>232</v>
-      </c>
       <c r="AA23" t="s" s="2">
         <v>81</v>
       </c>
@@ -4990,7 +4983,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>89</v>
@@ -5005,16 +4998,16 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>81</v>
@@ -5025,10 +5018,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5051,19 +5044,19 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="O24" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -5112,7 +5105,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -5130,13 +5123,13 @@
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>132</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>81</v>
@@ -5147,10 +5140,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5176,13 +5169,13 @@
         <v>109</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5208,13 +5201,13 @@
         <v>81</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>81</v>
@@ -5232,7 +5225,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -5250,10 +5243,10 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
@@ -5267,14 +5260,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5293,16 +5286,16 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5352,7 +5345,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5370,13 +5363,13 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>81</v>
@@ -5387,10 +5380,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5413,19 +5406,19 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5474,7 +5467,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5492,13 +5485,13 @@
         <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>81</v>
@@ -5509,10 +5502,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5535,16 +5528,16 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5594,7 +5587,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5612,10 +5605,10 @@
         <v>81</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
@@ -5629,10 +5622,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5655,16 +5648,16 @@
         <v>81</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5714,7 +5707,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5732,10 +5725,10 @@
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
@@ -5749,10 +5742,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5775,19 +5768,19 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>81</v>
@@ -5824,10 +5817,10 @@
         <v>81</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>81</v>
@@ -5836,7 +5829,7 @@
         <v>138</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5854,10 +5847,10 @@
         <v>81</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>81</v>
@@ -5871,10 +5864,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5897,13 +5890,13 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5954,7 +5947,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5975,7 +5968,7 @@
         <v>81</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
@@ -5989,14 +5982,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -6018,13 +6011,13 @@
         <v>134</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6065,7 +6058,7 @@
         <v>137</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>81</v>
@@ -6074,7 +6067,7 @@
         <v>138</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -6109,10 +6102,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6135,16 +6128,16 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6170,11 +6163,11 @@
         <v>81</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>81</v>
@@ -6192,7 +6185,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>89</v>
@@ -6213,7 +6206,7 @@
         <v>81</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>81</v>
@@ -6222,15 +6215,15 @@
         <v>81</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6253,13 +6246,13 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6286,31 +6279,31 @@
         <v>81</v>
       </c>
       <c r="X34" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="Z34" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="Y34" t="s" s="2">
+      <c r="AA34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>89</v>
@@ -6331,7 +6324,7 @@
         <v>81</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
@@ -6345,13 +6338,13 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>81</v>
@@ -6373,19 +6366,19 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="L35" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O35" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -6434,7 +6427,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6452,10 +6445,10 @@
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
@@ -6469,10 +6462,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6495,13 +6488,13 @@
         <v>81</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6552,7 +6545,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6573,7 +6566,7 @@
         <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
@@ -6587,14 +6580,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6616,13 +6609,13 @@
         <v>134</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6663,7 +6656,7 @@
         <v>137</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>81</v>
@@ -6672,7 +6665,7 @@
         <v>138</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6707,10 +6700,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6733,16 +6726,16 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6753,7 +6746,7 @@
         <v>81</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>81</v>
@@ -6768,11 +6761,11 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -6790,7 +6783,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>89</v>
@@ -6811,7 +6804,7 @@
         <v>81</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>81</v>
@@ -6820,15 +6813,15 @@
         <v>81</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6851,13 +6844,13 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6884,19 +6877,19 @@
         <v>81</v>
       </c>
       <c r="X39" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="Z39" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="Y39" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>318</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AC39" s="2"/>
       <c r="AD39" t="s" s="2">
@@ -6906,7 +6899,7 @@
         <v>138</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>89</v>
@@ -6927,7 +6920,7 @@
         <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>81</v>
@@ -6941,13 +6934,13 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>81</v>
@@ -6969,13 +6962,13 @@
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7002,11 +6995,11 @@
         <v>81</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
@@ -7024,7 +7017,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>89</v>
@@ -7045,7 +7038,7 @@
         <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>81</v>
@@ -7059,10 +7052,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7085,16 +7078,16 @@
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7120,13 +7113,13 @@
         <v>81</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>81</v>
@@ -7144,7 +7137,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7162,10 +7155,10 @@
         <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>81</v>
@@ -7179,10 +7172,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7205,16 +7198,16 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7264,7 +7257,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7282,16 +7275,16 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="AM42" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>347</v>
-      </c>
       <c r="AO42" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>81</v>
@@ -7299,14 +7292,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7325,17 +7318,17 @@
         <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -7384,7 +7377,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7402,16 +7395,16 @@
         <v>81</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>81</v>
@@ -7419,10 +7412,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7445,16 +7438,16 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7504,7 +7497,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7522,16 +7515,16 @@
         <v>81</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>81</v>
@@ -7539,10 +7532,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7565,19 +7558,19 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -7626,7 +7619,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7644,16 +7637,16 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>81</v>
@@ -7661,10 +7654,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7687,19 +7680,19 @@
         <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -7748,7 +7741,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7766,16 +7759,16 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>81</v>
@@ -7783,10 +7776,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7809,17 +7802,17 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -7844,13 +7837,13 @@
         <v>81</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>81</v>
@@ -7868,7 +7861,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7889,7 +7882,7 @@
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
@@ -7903,10 +7896,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7929,16 +7922,16 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7988,7 +7981,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7997,19 +7990,19 @@
         <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AK48" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AJ48" t="s" s="2">
+      <c r="AL48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -8023,10 +8016,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8049,13 +8042,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8106,7 +8099,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8127,7 +8120,7 @@
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
@@ -8141,10 +8134,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8222,7 +8215,7 @@
         <v>138</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8257,13 +8250,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B51" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="C51" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>81</v>
@@ -8285,16 +8278,16 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8344,7 +8337,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8379,13 +8372,13 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>81</v>
@@ -8407,7 +8400,7 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>144</v>
@@ -8464,7 +8457,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8499,13 +8492,13 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>81</v>
@@ -8527,16 +8520,16 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8586,7 +8579,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8607,7 +8600,7 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
@@ -8621,13 +8614,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>81</v>
@@ -8649,13 +8642,13 @@
         <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8706,7 +8699,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8741,13 +8734,13 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>81</v>
@@ -8769,16 +8762,16 @@
         <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8828,7 +8821,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8863,13 +8856,13 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>81</v>
@@ -8891,16 +8884,16 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8950,7 +8943,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8985,13 +8978,13 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>81</v>
@@ -9013,16 +9006,16 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9072,7 +9065,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -9107,13 +9100,13 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>81</v>
@@ -9135,13 +9128,13 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9192,7 +9185,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9227,13 +9220,13 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>81</v>
@@ -9255,16 +9248,16 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9314,7 +9307,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9349,13 +9342,13 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>81</v>
@@ -9377,16 +9370,16 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9436,7 +9429,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9471,13 +9464,13 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>81</v>
@@ -9499,19 +9492,19 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -9560,7 +9553,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9595,14 +9588,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9624,16 +9617,16 @@
         <v>134</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>81</v>
@@ -9682,7 +9675,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9717,10 +9710,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9743,19 +9736,19 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N63" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>81</v>
@@ -9804,7 +9797,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>89</v>
@@ -9816,16 +9809,16 @@
         <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>81</v>
@@ -9839,10 +9832,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9868,16 +9861,16 @@
         <v>103</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -9926,7 +9919,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9947,7 +9940,7 @@
         <v>81</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>81</v>
@@ -9961,10 +9954,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9987,19 +9980,19 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>81</v>
@@ -10024,13 +10017,13 @@
         <v>81</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>81</v>
@@ -10048,7 +10041,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -10057,7 +10050,7 @@
         <v>80</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>101</v>
@@ -10069,7 +10062,7 @@
         <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>81</v>
@@ -10083,14 +10076,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10109,19 +10102,19 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>81</v>
@@ -10170,7 +10163,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10185,13 +10178,13 @@
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>81</v>
@@ -10205,10 +10198,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10231,16 +10224,16 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10290,7 +10283,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10305,13 +10298,13 @@
         <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>81</v>
@@ -10325,10 +10318,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10354,16 +10347,16 @@
         <v>109</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>81</v>
@@ -10388,13 +10381,13 @@
         <v>81</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>81</v>
@@ -10412,7 +10405,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>89</v>
@@ -10427,13 +10420,13 @@
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>81</v>
@@ -10447,10 +10440,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10473,19 +10466,19 @@
         <v>81</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>81</v>
@@ -10534,7 +10527,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10546,7 +10539,7 @@
         <v>81</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>81</v>
@@ -10555,7 +10548,7 @@
         <v>81</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>81</v>
@@ -10569,10 +10562,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10595,13 +10588,13 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10652,7 +10645,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10673,7 +10666,7 @@
         <v>81</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>81</v>
@@ -10687,14 +10680,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10716,13 +10709,13 @@
         <v>134</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10772,7 +10765,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10793,7 +10786,7 @@
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
@@ -10807,14 +10800,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10836,16 +10829,16 @@
         <v>134</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -10894,7 +10887,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10929,10 +10922,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10955,16 +10948,16 @@
         <v>81</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11014,7 +11007,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>89</v>
@@ -11035,7 +11028,7 @@
         <v>81</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>81</v>
@@ -11049,10 +11042,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11078,10 +11071,10 @@
         <v>109</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11108,13 +11101,13 @@
         <v>81</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>81</v>
@@ -11132,7 +11125,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>89</v>
@@ -11153,7 +11146,7 @@
         <v>81</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>81</v>
@@ -11167,10 +11160,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11193,13 +11186,13 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11226,40 +11219,40 @@
         <v>81</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="Y75" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI75" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>101</v>
@@ -11271,7 +11264,7 @@
         <v>81</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>81</v>
@@ -11285,10 +11278,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11314,13 +11307,13 @@
         <v>109</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11346,14 +11339,14 @@
         <v>81</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="Y76" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="Z76" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="Z76" t="s" s="2">
-        <v>519</v>
-      </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
       </c>
@@ -11370,7 +11363,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11379,7 +11372,7 @@
         <v>89</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>101</v>
@@ -11391,7 +11384,7 @@
         <v>81</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>81</v>
@@ -11405,10 +11398,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11431,23 +11424,23 @@
         <v>81</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="N77" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q77" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="R77" t="s" s="2">
         <v>81</v>
@@ -11492,7 +11485,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11501,19 +11494,19 @@
         <v>89</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>81</v>
@@ -11527,10 +11520,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11553,26 +11546,26 @@
         <v>81</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="N78" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="P78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q78" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="O78" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="P78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q78" t="s" s="2">
-        <v>533</v>
-      </c>
       <c r="R78" t="s" s="2">
         <v>81</v>
       </c>
@@ -11616,7 +11609,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11625,19 +11618,19 @@
         <v>89</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>81</v>
@@ -11651,10 +11644,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11677,19 +11670,19 @@
         <v>81</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="N79" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="O79" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>81</v>
@@ -11738,7 +11731,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11747,19 +11740,19 @@
         <v>89</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>81</v>
@@ -11773,10 +11766,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11799,16 +11792,16 @@
         <v>81</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11858,7 +11851,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11867,19 +11860,19 @@
         <v>89</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>81</v>
@@ -11893,10 +11886,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11919,16 +11912,16 @@
         <v>81</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11978,7 +11971,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11987,19 +11980,19 @@
         <v>89</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>81</v>
@@ -12013,10 +12006,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12039,16 +12032,16 @@
         <v>81</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12098,7 +12091,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -12107,7 +12100,7 @@
         <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>101</v>
@@ -12119,7 +12112,7 @@
         <v>81</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>81</v>
@@ -12133,10 +12126,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12159,13 +12152,13 @@
         <v>81</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12216,7 +12209,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12237,7 +12230,7 @@
         <v>81</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>81</v>
@@ -12251,14 +12244,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12280,13 +12273,13 @@
         <v>134</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12336,7 +12329,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12357,7 +12350,7 @@
         <v>81</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>81</v>
@@ -12371,14 +12364,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12400,16 +12393,16 @@
         <v>134</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>81</v>
@@ -12458,7 +12451,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12493,10 +12486,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12519,16 +12512,16 @@
         <v>81</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12554,13 +12547,13 @@
         <v>81</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>81</v>
@@ -12578,7 +12571,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>89</v>
@@ -12599,7 +12592,7 @@
         <v>81</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>81</v>
@@ -12613,10 +12606,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12639,23 +12632,23 @@
         <v>81</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="N87" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q87" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="R87" t="s" s="2">
         <v>81</v>
@@ -12700,7 +12693,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12721,7 +12714,7 @@
         <v>81</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
@@ -12735,10 +12728,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12761,19 +12754,19 @@
         <v>81</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N88" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>577</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>81</v>
@@ -12822,7 +12815,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12831,7 +12824,7 @@
         <v>80</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>101</v>
@@ -12843,7 +12836,7 @@
         <v>81</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>81</v>
@@ -12857,10 +12850,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12883,13 +12876,13 @@
         <v>81</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12940,7 +12933,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12961,7 +12954,7 @@
         <v>81</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
@@ -12975,14 +12968,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13004,13 +12997,13 @@
         <v>134</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13060,7 +13053,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -13081,7 +13074,7 @@
         <v>81</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>81</v>
@@ -13095,14 +13088,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13124,16 +13117,16 @@
         <v>134</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -13182,7 +13175,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13217,10 +13210,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13243,16 +13236,16 @@
         <v>81</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13278,13 +13271,13 @@
         <v>81</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>81</v>
@@ -13302,7 +13295,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>89</v>
@@ -13317,13 +13310,13 @@
         <v>101</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>81</v>
@@ -13337,10 +13330,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13366,16 +13359,16 @@
         <v>82</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="N93" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -13424,7 +13417,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13433,19 +13426,19 @@
         <v>80</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>81</v>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-location.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-questionnaire-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T16:44:46+00:00</t>
+    <t>2026-02-09T14:48:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
